--- a/presentations/heatmap_byhand/xlsx/baseline_methods/owasp_aivss/mcp_sqlite_risk_rankings_aivss.xlsx
+++ b/presentations/heatmap_byhand/xlsx/baseline_methods/owasp_aivss/mcp_sqlite_risk_rankings_aivss.xlsx
@@ -1767,12 +1767,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1791,6 +1792,11 @@
           <t>Risk Level</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
@@ -1806,6 +1812,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>scale=0.30 TU×PIS; Credentials 9.5×0.30×1.15×1.10=3.6 → Medium</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
@@ -1821,6 +1832,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>scale=0.40 TU×PIS; Credentials 9.5×0.40×1.15×1.10=4.8 → Medium</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -1836,6 +1852,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>scale=0.95 TU×DA×MSR×PIS; Credentials 9.5×0.95×1.15×1.10×1.10×1.10=14.4→10 → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
@@ -1851,6 +1872,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>scale=1.00 TU×PM×MSR; Credentials 9.5×1.00×1.15×1.10×1.10=13.3→10 → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -1866,6 +1892,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>scale=0.60 TU×PM; Credentials 9.5×0.60×1.15×1.10=7.2 → High</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="13" t="n">
@@ -1879,6 +1910,11 @@
       <c r="C7" s="10" t="inlineStr">
         <is>
           <t>High</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>scale=0.65 TU×PM×MSR; PII 9.0×0.65×1.15×1.10×1.10=8.1 → High</t>
         </is>
       </c>
     </row>
@@ -1894,12 +1930,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1918,6 +1955,11 @@
           <t>Risk Level</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
@@ -1933,6 +1975,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>data_base=9.0; read_query TU×DA×MSR×PIS → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
@@ -1948,6 +1995,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>data_base=8.5; read_query TU×DA×MSR×PIS → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -1963,6 +2015,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>data_base=9.5; highest base; all amplified tools → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
@@ -1978,6 +2035,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>data_base=5.5; read_query TU×DA×MSR×PIS → High</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
@@ -1993,6 +2055,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>data_base=2.5; all tools stay Low-Medium after amplification</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -2008,6 +2075,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>data_base=4.5; write_query TU×PM×MSR=4.5×1.00×1.15×1.10×1.10=6.3 → Medium</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -2021,6 +2093,11 @@
       <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Low</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>data_base=3.0; write_query 3.0×1.00×1.15×1.10×1.10=4.2 → Medium; read 3.0×0.95×…=Low-Med</t>
         </is>
       </c>
     </row>
@@ -2035,12 +2112,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2059,6 +2137,11 @@
           <t>Risk Level</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Reasoning</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
@@ -2074,6 +2157,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PII+Financial rows: read_query TU×DA×MSR×PIS on base=9.0/8.5 → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
@@ -2089,6 +2177,11 @@
           <t>Medium</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Research Metadata base=4.0; write_query TU×PM×MSR=4.0×1.15×1.10×1.10=5.6 → Medium</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -2104,6 +2197,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Internal Data base=5.0; read_query TU×DA×MSR×PIS → High</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
@@ -2119,6 +2217,11 @@
           <t>High</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Research Results base=5.5; read_query amplified → High</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -2134,6 +2237,11 @@
           <t>Low</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Public Output base=2.0; all tools amplified stay Low after TU → Low</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
@@ -2149,6 +2257,11 @@
           <t>Critical</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Financial base=8.5; read_query amplified → Critical</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -2162,6 +2275,11 @@
       <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Critical</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Credentials base=9.5; highest base; all amplified tools → Critical</t>
         </is>
       </c>
     </row>
